--- a/Docs/Euro Fund-Moviment.xlsx
+++ b/Docs/Euro Fund-Moviment.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Repositoris\C#\_Actiu\InversionsV2\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003F440A-5AEF-483D-88B8-94219CE8B533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059A7A15-7354-491D-93EB-DF4567525010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-20" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{67C9267C-8DE9-4BF2-8230-BF48900302D9}"/>
+    <workbookView xWindow="22932" yWindow="0" windowWidth="23256" windowHeight="12576" xr2:uid="{67C9267C-8DE9-4BF2-8230-BF48900302D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Orig Vendes Reals" sheetId="3" r:id="rId3"/>
+    <sheet name="Orig Vendes Reals Nou Ordre" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,8 +27,118 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>joanp</author>
+  </authors>
+  <commentList>
+    <comment ref="Q2" authorId="0" shapeId="0" xr:uid="{9A1E5F51-DF95-436D-9D00-96B469684644}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Ha de ser: 1,836,64€
+Segons SelfBank</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q4" authorId="0" shapeId="0" xr:uid="{58BF279D-6CE1-4B45-A693-17D2141C3F05}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Ha de ser: 1,836,64€
+Segons SelfBank</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>joanp</author>
+  </authors>
+  <commentList>
+    <comment ref="Q2" authorId="0" shapeId="0" xr:uid="{F6A50562-AD83-4E47-9B1F-F9A50D0391B3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Ha de ser: 1,836,64€
+Segons SelfBank</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q4" authorId="0" shapeId="0" xr:uid="{77BC1215-5948-44D1-BB30-5599AA2F7A61}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Ha de ser: 1,836,64€
+Segons SelfBank</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q7" authorId="0" shapeId="0" xr:uid="{750614EB-B30D-4D9F-9B7B-CF256E9A34A1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Ha de ser: 1,836,64€
+Segons SelfBank</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q35" authorId="0" shapeId="0" xr:uid="{954B9F36-6C47-4D1B-B6C8-91690C83AA3D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Ha de ser: 1,836,64€
+Segons SelfBank</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="50">
   <si>
     <t>Traspàs C</t>
   </si>
@@ -101,17 +213,98 @@
   </si>
   <si>
     <t>PiG en cartera</t>
+  </si>
+  <si>
+    <t>Parts Orig</t>
+  </si>
+  <si>
+    <t>Parts Orig Ut</t>
+  </si>
+  <si>
+    <t>Parts en cartera</t>
+  </si>
+  <si>
+    <t>Parts orig en cartera</t>
+  </si>
+  <si>
+    <t>PiG Orig en cartera</t>
+  </si>
+  <si>
+    <t>PU Orig</t>
+  </si>
+  <si>
+    <t>Import Orig venda real</t>
+  </si>
+  <si>
+    <t>Pig Origen venda real</t>
+  </si>
+  <si>
+    <t>Nom Fons Orig</t>
+  </si>
+  <si>
+    <t>Bolsa Tecnología y Telecomunicaciones FI</t>
+  </si>
+  <si>
+    <t>Optimal Income A-H Grs Acc Hdg EUR</t>
+  </si>
+  <si>
+    <t>Biotechnology C USD Acc</t>
+  </si>
+  <si>
+    <t>European Growth N Acc ?</t>
+  </si>
+  <si>
+    <t>Trea Renta Fija Ahorro S FI</t>
+  </si>
+  <si>
+    <t>Data Compra Venda</t>
+  </si>
+  <si>
+    <t>Import Orig en cartera</t>
+  </si>
+  <si>
+    <t>Data compra</t>
+  </si>
+  <si>
+    <t>Import</t>
+  </si>
+  <si>
+    <t>Data venda</t>
+  </si>
+  <si>
+    <t>Venda 1278 segons SelfBank</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Mov</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Pig SelfBank</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="8">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="164" formatCode="#,##0.000\ &quot;€&quot;;[Red]\-#,##0.000\ &quot;€&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000\ &quot;€&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000\ &quot;€&quot;"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,16 +320,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -144,11 +362,91 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -172,6 +470,75 @@
     </xf>
     <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -490,29 +857,32 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="6" max="6" width="1.7265625" customWidth="1"/>
     <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.1796875" customWidth="1"/>
     <col min="10" max="10" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="D1" t="s">
+      <c r="D1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="55" t="s">
         <v>22</v>
       </c>
     </row>
@@ -548,9 +918,9 @@
         <f>(E9-E2)*D9</f>
         <v>421.92276719999984</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="10">
         <f>(E$10-E2)*I2</f>
-        <v>145.37891520000011</v>
+        <v>147.88398239999987</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
@@ -581,9 +951,9 @@
         <f>D3</f>
         <v>34.723999999999997</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="10">
         <f>(E$10-E3)*I3</f>
-        <v>860.42252360000066</v>
+        <v>875.15591679999932</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -614,9 +984,9 @@
         <f t="shared" ref="I4:I8" si="2">D4</f>
         <v>46.265999999999998</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="10">
         <f t="shared" ref="K4:K8" si="3">(E$10-E4)*I4</f>
-        <v>1155.1694880000007</v>
+        <v>1174.800151799999</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
@@ -647,9 +1017,9 @@
         <f t="shared" si="2"/>
         <v>23.23</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="10">
         <f t="shared" si="3"/>
-        <v>614.26159800000062</v>
+        <v>624.11808699999972</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -680,9 +1050,9 @@
         <f t="shared" si="2"/>
         <v>21.81</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="10">
         <f t="shared" si="3"/>
-        <v>571.54849800000022</v>
+        <v>580.80248099999937</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -713,9 +1083,9 @@
         <f t="shared" si="2"/>
         <v>18.635999999999999</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="10">
         <f t="shared" si="3"/>
-        <v>487.96129680000035</v>
+        <v>495.86855159999959</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -746,9 +1116,9 @@
         <f t="shared" si="2"/>
         <v>5.8719999999999999</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="10">
         <f t="shared" si="3"/>
-        <v>148.41362560000016</v>
+        <v>150.90511519999993</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -786,11 +1156,11 @@
         <v>156.44199999999998</v>
       </c>
       <c r="E10" s="4">
-        <v>459.72570000000002</v>
+        <v>460.15</v>
       </c>
       <c r="H10" s="4">
         <f>D10*E10</f>
-        <v>71920.407959399992</v>
+        <v>71986.786299999992</v>
       </c>
       <c r="I10" s="4"/>
     </row>
@@ -801,7 +1171,7 @@
       </c>
       <c r="K11" s="4">
         <f>SUM(K2:K9)</f>
-        <v>3983.1559452000029</v>
+        <v>4049.5342857999967</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -810,7 +1180,7 @@
       </c>
       <c r="K12" s="9">
         <f>+J11+K11</f>
-        <v>4405.0787124000026</v>
+        <v>4471.4570529999964</v>
       </c>
     </row>
   </sheetData>
@@ -1309,4 +1679,2127 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12067BC-D477-473D-98A4-83F12DFA1D93}">
+  <dimension ref="A1:T28"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" customWidth="1"/>
+    <col min="4" max="4" width="6.81640625" customWidth="1"/>
+    <col min="5" max="5" width="11.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6328125" style="46" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.6328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.6328125" customWidth="1"/>
+    <col min="17" max="17" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.90625" customWidth="1"/>
+    <col min="19" max="20" width="10.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="M1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="19">
+        <v>1239</v>
+      </c>
+      <c r="C2" s="19">
+        <v>15</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="20">
+        <v>44893.572569444441</v>
+      </c>
+      <c r="F2" s="20">
+        <v>36841</v>
+      </c>
+      <c r="G2" s="43">
+        <v>18.6356</v>
+      </c>
+      <c r="H2" s="21">
+        <v>321.66890000000001</v>
+      </c>
+      <c r="I2" s="43">
+        <f>I3</f>
+        <v>18.6356</v>
+      </c>
+      <c r="J2" s="21">
+        <f>H2/G2*I2</f>
+        <v>321.66890000000001</v>
+      </c>
+      <c r="K2" s="21">
+        <f>G2-I2</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="21">
+        <f>H2-J2</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="22">
+        <v>433.54192724694099</v>
+      </c>
+      <c r="N2" s="22">
+        <v>22.9920399034783</v>
+      </c>
+      <c r="O2" s="22">
+        <f>$N2*J2</f>
+        <v>7395.824184507971</v>
+      </c>
+      <c r="P2" s="22">
+        <f>$N2*L2</f>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="22">
+        <f>I3*M3-O2</f>
+        <v>1134.4744942520292</v>
+      </c>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22">
+        <f>S$3/G3*G2</f>
+        <v>1836.6005786649498</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="23">
+        <v>1278</v>
+      </c>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="24">
+        <v>45495.441631944443</v>
+      </c>
+      <c r="F3" s="24"/>
+      <c r="G3" s="44">
+        <v>18.635999999999999</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="44">
+        <f>G2</f>
+        <v>18.6356</v>
+      </c>
+      <c r="J3" s="25"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="26">
+        <v>457.74209999999999</v>
+      </c>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="26">
+        <v>1836.64</v>
+      </c>
+      <c r="T3" s="13"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="19">
+        <v>1239</v>
+      </c>
+      <c r="C4" s="19">
+        <v>16</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="20">
+        <v>44893.572569444441</v>
+      </c>
+      <c r="F4" s="20">
+        <v>41166</v>
+      </c>
+      <c r="G4" s="43">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="H4" s="21">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="I4" s="43">
+        <f>I5</f>
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="J4" s="21">
+        <f>H4/G4*I4</f>
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="K4" s="21">
+        <f>G4-I4</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="21">
+        <f>H4-J4</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="22">
+        <v>433.54192724694099</v>
+      </c>
+      <c r="N4" s="22">
+        <v>18.259999998612201</v>
+      </c>
+      <c r="O4" s="22">
+        <f>$N4*J4</f>
+        <v>5.295399999597538E-2</v>
+      </c>
+      <c r="P4" s="22">
+        <f>$N4*L4</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="22">
+        <f>I5*M5-O4</f>
+        <v>0.13014284000402462</v>
+      </c>
+      <c r="R4" s="19"/>
+      <c r="S4" s="22">
+        <f>S$3/G5*G4</f>
+        <v>3.9421335050440015E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="23">
+        <v>1278</v>
+      </c>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="24">
+        <v>45495.441631944443</v>
+      </c>
+      <c r="F5" s="24"/>
+      <c r="G5" s="44">
+        <v>18.635999999999999</v>
+      </c>
+      <c r="H5" s="25"/>
+      <c r="I5" s="44">
+        <f>G4</f>
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="26">
+        <v>457.74209999999999</v>
+      </c>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="26">
+        <v>1836.64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="48">
+        <v>1241</v>
+      </c>
+      <c r="C6" s="48">
+        <v>16</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="49">
+        <v>44939.567002314812</v>
+      </c>
+      <c r="F6" s="49">
+        <v>41166</v>
+      </c>
+      <c r="G6" s="50">
+        <v>2.0112999999999999</v>
+      </c>
+      <c r="H6" s="51">
+        <v>14.956799999999999</v>
+      </c>
+      <c r="I6" s="50"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="50">
+        <f t="shared" ref="K6:L8" si="0">G6</f>
+        <v>2.0112999999999999</v>
+      </c>
+      <c r="L6" s="50">
+        <f t="shared" si="0"/>
+        <v>14.956799999999999</v>
+      </c>
+      <c r="M6" s="52">
+        <v>434.45088886239699</v>
+      </c>
+      <c r="N6" s="52">
+        <v>18.259999998612201</v>
+      </c>
+      <c r="O6" s="52">
+        <f>$N6*J6</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="52">
+        <f>$N6*L6</f>
+        <v>273.11116797924296</v>
+      </c>
+      <c r="Q6" s="52">
+        <f>I7*M7-O6</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="53">
+        <f>K6*M$16-P6</f>
+        <v>652.38772250075704</v>
+      </c>
+      <c r="S6" s="52"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="19">
+        <v>217</v>
+      </c>
+      <c r="C7" s="19">
+        <v>16</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="20">
+        <v>44725.295381944445</v>
+      </c>
+      <c r="F7" s="20">
+        <v>41166</v>
+      </c>
+      <c r="G7" s="43">
+        <v>23.23</v>
+      </c>
+      <c r="H7" s="21">
+        <v>152.5463</v>
+      </c>
+      <c r="I7" s="43"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="43">
+        <f t="shared" si="0"/>
+        <v>23.23</v>
+      </c>
+      <c r="L7" s="43">
+        <f t="shared" si="0"/>
+        <v>152.5463</v>
+      </c>
+      <c r="M7" s="22">
+        <v>433.283090830822</v>
+      </c>
+      <c r="N7" s="22">
+        <v>18.259999998612201</v>
+      </c>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="22"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="19">
+        <v>1235</v>
+      </c>
+      <c r="C8" s="19">
+        <v>16</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="20">
+        <v>44893.559050925927</v>
+      </c>
+      <c r="F8" s="20">
+        <v>41166</v>
+      </c>
+      <c r="G8" s="43">
+        <v>21.81</v>
+      </c>
+      <c r="H8" s="21">
+        <v>158.67240000000001</v>
+      </c>
+      <c r="I8" s="43"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="43">
+        <f t="shared" si="0"/>
+        <v>21.81</v>
+      </c>
+      <c r="L8" s="43">
+        <f t="shared" si="0"/>
+        <v>158.67240000000001</v>
+      </c>
+      <c r="M8" s="22">
+        <v>433.51991556808798</v>
+      </c>
+      <c r="N8" s="22">
+        <v>18.259999998612201</v>
+      </c>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="22"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="19">
+        <v>197</v>
+      </c>
+      <c r="C9" s="19">
+        <v>17</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="20">
+        <v>44473.584976851853</v>
+      </c>
+      <c r="F9" s="20">
+        <v>41377</v>
+      </c>
+      <c r="G9" s="43">
+        <v>24.54</v>
+      </c>
+      <c r="H9" s="21">
+        <v>226.48509999999999</v>
+      </c>
+      <c r="I9" s="43"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="43">
+        <f t="shared" ref="K9:K15" si="1">G9</f>
+        <v>24.54</v>
+      </c>
+      <c r="L9" s="43">
+        <f t="shared" ref="L9:L15" si="2">H9</f>
+        <v>226.48509999999999</v>
+      </c>
+      <c r="M9" s="22">
+        <v>435.10187449062698</v>
+      </c>
+      <c r="N9" s="22">
+        <v>19.7899983277443</v>
+      </c>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="22"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="48">
+        <v>1241</v>
+      </c>
+      <c r="C10" s="48">
+        <v>17</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="49">
+        <v>44939.567002314812</v>
+      </c>
+      <c r="F10" s="49">
+        <v>41377</v>
+      </c>
+      <c r="G10" s="50">
+        <v>1.1525000000000001</v>
+      </c>
+      <c r="H10" s="51">
+        <v>18.2224</v>
+      </c>
+      <c r="I10" s="50"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="50">
+        <f t="shared" si="1"/>
+        <v>1.1525000000000001</v>
+      </c>
+      <c r="L10" s="50">
+        <f t="shared" si="2"/>
+        <v>18.2224</v>
+      </c>
+      <c r="M10" s="52">
+        <v>434.45088886239699</v>
+      </c>
+      <c r="N10" s="52">
+        <v>19.7899983277443</v>
+      </c>
+      <c r="O10" s="52">
+        <f>$N10*J10</f>
+        <v>0</v>
+      </c>
+      <c r="P10" s="52">
+        <f>$N10*L10</f>
+        <v>360.62126552748776</v>
+      </c>
+      <c r="Q10" s="52">
+        <f>I11*M11-O10</f>
+        <v>0</v>
+      </c>
+      <c r="R10" s="53">
+        <f>K10*M$16-P10</f>
+        <v>169.70114847251233</v>
+      </c>
+      <c r="S10" s="52"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="19">
+        <v>205</v>
+      </c>
+      <c r="C11" s="19">
+        <v>17</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="20">
+        <v>44524.517384259256</v>
+      </c>
+      <c r="F11" s="20">
+        <v>41377</v>
+      </c>
+      <c r="G11" s="43">
+        <v>46.265999999999998</v>
+      </c>
+      <c r="H11" s="21">
+        <v>396.34890000000001</v>
+      </c>
+      <c r="I11" s="43"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="43">
+        <f t="shared" si="1"/>
+        <v>46.265999999999998</v>
+      </c>
+      <c r="L11" s="43">
+        <f t="shared" si="2"/>
+        <v>396.34890000000001</v>
+      </c>
+      <c r="M11" s="22">
+        <v>434.75770544244102</v>
+      </c>
+      <c r="N11" s="22">
+        <v>19.7899983277443</v>
+      </c>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="22"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="19">
+        <v>203</v>
+      </c>
+      <c r="C12" s="19">
+        <v>7</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="20">
+        <v>44496.480810185189</v>
+      </c>
+      <c r="F12" s="20">
+        <v>41492.000011574077</v>
+      </c>
+      <c r="G12" s="43">
+        <v>29.760999999999999</v>
+      </c>
+      <c r="H12" s="21">
+        <v>22.006</v>
+      </c>
+      <c r="I12" s="43"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="43">
+        <f t="shared" si="1"/>
+        <v>29.760999999999999</v>
+      </c>
+      <c r="L12" s="43">
+        <f t="shared" si="2"/>
+        <v>22.006</v>
+      </c>
+      <c r="M12" s="22">
+        <v>434.94679414813902</v>
+      </c>
+      <c r="N12" s="22">
+        <v>250.44122530300501</v>
+      </c>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="22"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="48">
+        <v>1241</v>
+      </c>
+      <c r="C13" s="48">
+        <v>27</v>
+      </c>
+      <c r="D13" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="49">
+        <v>44939.567002314812</v>
+      </c>
+      <c r="F13" s="49">
+        <v>41521</v>
+      </c>
+      <c r="G13" s="50">
+        <v>0.64380000000000004</v>
+      </c>
+      <c r="H13" s="51">
+        <v>13.0237</v>
+      </c>
+      <c r="I13" s="50"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="50">
+        <f t="shared" si="1"/>
+        <v>0.64380000000000004</v>
+      </c>
+      <c r="L13" s="50">
+        <f t="shared" si="2"/>
+        <v>13.0237</v>
+      </c>
+      <c r="M13" s="52">
+        <v>434.45088886239699</v>
+      </c>
+      <c r="N13" s="52">
+        <v>17.093261768828398</v>
+      </c>
+      <c r="O13" s="52">
+        <f>$N13*J13</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="52">
+        <f>$N13*L13</f>
+        <v>222.6175132986904</v>
+      </c>
+      <c r="Q13" s="52">
+        <f>I14*M14-O13</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="53">
+        <f>K13*M$16-P13</f>
+        <v>73.626799181309622</v>
+      </c>
+      <c r="S13" s="52"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="19">
+        <v>203</v>
+      </c>
+      <c r="C14" s="19">
+        <v>37</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="20">
+        <v>44496.480810185189</v>
+      </c>
+      <c r="F14" s="20">
+        <v>41534</v>
+      </c>
+      <c r="G14" s="43">
+        <v>4.9630000000000001</v>
+      </c>
+      <c r="H14" s="21">
+        <v>76.745999999999995</v>
+      </c>
+      <c r="I14" s="43"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="43">
+        <f t="shared" si="1"/>
+        <v>4.9630000000000001</v>
+      </c>
+      <c r="L14" s="43">
+        <f t="shared" si="2"/>
+        <v>76.745999999999995</v>
+      </c>
+      <c r="M14" s="22">
+        <v>434.94679414813902</v>
+      </c>
+      <c r="N14" s="22">
+        <v>13.029995048601901</v>
+      </c>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="22"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="48">
+        <v>1241</v>
+      </c>
+      <c r="C15" s="48">
+        <v>108</v>
+      </c>
+      <c r="D15" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="49">
+        <v>44939.567002314812</v>
+      </c>
+      <c r="F15" s="49">
+        <v>42387.492534722223</v>
+      </c>
+      <c r="G15" s="50">
+        <v>2.0644</v>
+      </c>
+      <c r="H15" s="51">
+        <v>0.53749999999999998</v>
+      </c>
+      <c r="I15" s="50"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="50">
+        <f t="shared" si="1"/>
+        <v>2.0644</v>
+      </c>
+      <c r="L15" s="50">
+        <f t="shared" si="2"/>
+        <v>0.53749999999999998</v>
+      </c>
+      <c r="M15" s="52">
+        <v>434.45088886239699</v>
+      </c>
+      <c r="N15" s="52">
+        <v>1860.4651162790601</v>
+      </c>
+      <c r="O15" s="52">
+        <f>$N15*J15</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="52">
+        <f>$N15*L15</f>
+        <v>999.99999999999477</v>
+      </c>
+      <c r="Q15" s="52">
+        <f>I16*M16-O15</f>
+        <v>0</v>
+      </c>
+      <c r="R15" s="53">
+        <f>K15*M$16-P15</f>
+        <v>-50.067165759994737</v>
+      </c>
+      <c r="S15" s="52"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="M16" s="27">
+        <v>460.14960000000002</v>
+      </c>
+      <c r="R16" s="47">
+        <f>SUM(R6:R15)</f>
+        <v>845.64850439458428</v>
+      </c>
+    </row>
+    <row r="17" spans="6:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q17" s="13"/>
+    </row>
+    <row r="18" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F18" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="30"/>
+      <c r="H18" s="31"/>
+    </row>
+    <row r="19" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F19" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="H19" s="41" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F20" s="34">
+        <v>36871</v>
+      </c>
+      <c r="G20" s="12">
+        <v>7.1680000000000001</v>
+      </c>
+      <c r="H20" s="35">
+        <v>3087.53</v>
+      </c>
+    </row>
+    <row r="21" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F21" s="34">
+        <v>36889</v>
+      </c>
+      <c r="G21" s="12">
+        <v>9.6880000000000006</v>
+      </c>
+      <c r="H21" s="35">
+        <v>3005.06</v>
+      </c>
+    </row>
+    <row r="22" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F22" s="34">
+        <v>36913</v>
+      </c>
+      <c r="G22" s="12">
+        <v>1.778</v>
+      </c>
+      <c r="H22" s="35">
+        <v>601.01</v>
+      </c>
+    </row>
+    <row r="23" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F23" s="34">
+        <v>41169</v>
+      </c>
+      <c r="G23" s="12">
+        <v>2E-3</v>
+      </c>
+      <c r="H23" s="35">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="24" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F24" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="33">
+        <f>SUM(G20:G23)</f>
+        <v>18.635999999999999</v>
+      </c>
+      <c r="H24" s="36">
+        <f>SUM(H20:H23)</f>
+        <v>6693.83</v>
+      </c>
+    </row>
+    <row r="25" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F25" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="H25" s="41" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F26" s="34">
+        <v>45495</v>
+      </c>
+      <c r="G26" s="12">
+        <v>18.635999999999999</v>
+      </c>
+      <c r="H26" s="35">
+        <v>8530.48</v>
+      </c>
+    </row>
+    <row r="27" spans="6:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F27" s="37"/>
+      <c r="G27" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="39">
+        <f>H26-H24</f>
+        <v>1836.6499999999996</v>
+      </c>
+    </row>
+    <row r="28" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="H28" s="28"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{686C5B57-6B90-4E80-BE9A-01DAF3ED59FE}">
+  <dimension ref="A1:U38"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" customWidth="1"/>
+    <col min="4" max="4" width="6.81640625" customWidth="1"/>
+    <col min="5" max="5" width="11.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6328125" style="46" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.6328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.6328125" customWidth="1"/>
+    <col min="17" max="17" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.90625" customWidth="1"/>
+    <col min="19" max="20" width="10.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="M1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="19">
+        <v>1239</v>
+      </c>
+      <c r="C2" s="19">
+        <v>15</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="20">
+        <v>44893.572569444441</v>
+      </c>
+      <c r="F2" s="20">
+        <v>36841</v>
+      </c>
+      <c r="G2" s="43">
+        <v>18.6356</v>
+      </c>
+      <c r="H2" s="21">
+        <v>321.66890000000001</v>
+      </c>
+      <c r="I2" s="43">
+        <f>I3</f>
+        <v>18.6356</v>
+      </c>
+      <c r="J2" s="21">
+        <f>H2/G2*I2</f>
+        <v>321.66890000000001</v>
+      </c>
+      <c r="K2" s="43">
+        <f>G2-I2</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="43">
+        <f>H2/G2*K2</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="22">
+        <v>433.54192724694099</v>
+      </c>
+      <c r="N2" s="22">
+        <v>22.9920399034783</v>
+      </c>
+      <c r="O2" s="22">
+        <f>$N2*J2</f>
+        <v>7395.824184507971</v>
+      </c>
+      <c r="P2" s="22">
+        <f>$N2*L2</f>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="22">
+        <f>I3*M3-O2</f>
+        <v>1134.4744942520292</v>
+      </c>
+      <c r="R2" s="43">
+        <f>(G2-I2)*M14-P2</f>
+        <v>0</v>
+      </c>
+      <c r="S2" s="22">
+        <f>S$3/G3*G2</f>
+        <v>1836.6005786649498</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="23">
+        <v>1278</v>
+      </c>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="24">
+        <v>45495.441631944443</v>
+      </c>
+      <c r="F3" s="24"/>
+      <c r="G3" s="44">
+        <v>18.635999999999999</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="44">
+        <f>G2</f>
+        <v>18.6356</v>
+      </c>
+      <c r="J3" s="25"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="26">
+        <v>457.74209999999999</v>
+      </c>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="26">
+        <v>1836.64</v>
+      </c>
+      <c r="T3" s="13"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="19">
+        <v>217</v>
+      </c>
+      <c r="C4" s="19">
+        <v>16</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="20">
+        <v>44725.295381944445</v>
+      </c>
+      <c r="F4" s="20">
+        <v>41166</v>
+      </c>
+      <c r="G4" s="43">
+        <v>23.23</v>
+      </c>
+      <c r="H4" s="21">
+        <v>152.5463</v>
+      </c>
+      <c r="I4" s="43">
+        <f>I5</f>
+        <v>3.9999999999906777E-4</v>
+      </c>
+      <c r="J4" s="21">
+        <f>H4/G4*I4</f>
+        <v>2.6267120103253458E-3</v>
+      </c>
+      <c r="K4" s="43">
+        <f>G4-I4</f>
+        <v>23.229600000000001</v>
+      </c>
+      <c r="L4" s="43">
+        <f>H4/G4*K4</f>
+        <v>152.54367328798966</v>
+      </c>
+      <c r="M4" s="22">
+        <v>433.283090830822</v>
+      </c>
+      <c r="N4" s="22">
+        <v>18.259999998612201</v>
+      </c>
+      <c r="O4" s="22">
+        <f>$N4*J4</f>
+        <v>4.7963761304895471E-2</v>
+      </c>
+      <c r="P4" s="22">
+        <f>$N4*L4</f>
+        <v>2785.4474740269911</v>
+      </c>
+      <c r="Q4" s="22">
+        <f>I4*M5-O4</f>
+        <v>0.13513307869467781</v>
+      </c>
+      <c r="R4" s="43">
+        <f>K4*M16-P4</f>
+        <v>7903.6436741330108</v>
+      </c>
+      <c r="S4" s="22">
+        <f>S$3/G5*I4</f>
+        <v>3.9421335050348137E-2</v>
+      </c>
+      <c r="T4" s="13">
+        <f>+Q4+R4</f>
+        <v>7903.7788072117055</v>
+      </c>
+      <c r="U4" s="54">
+        <v>7903.7879999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="23">
+        <v>1278</v>
+      </c>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="24">
+        <v>45495.441631944443</v>
+      </c>
+      <c r="F5" s="24"/>
+      <c r="G5" s="44">
+        <v>18.635999999999999</v>
+      </c>
+      <c r="H5" s="25"/>
+      <c r="I5" s="44">
+        <f>G5-I3</f>
+        <v>3.9999999999906777E-4</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="26">
+        <v>457.74209999999999</v>
+      </c>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="26">
+        <v>1836.64</v>
+      </c>
+      <c r="U5" s="13">
+        <f>+U4-T4</f>
+        <v>9.1927882940581185E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="19">
+        <v>1235</v>
+      </c>
+      <c r="C6" s="19">
+        <v>16</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="20">
+        <v>44893.559050925927</v>
+      </c>
+      <c r="F6" s="20">
+        <v>41166</v>
+      </c>
+      <c r="G6" s="43">
+        <v>21.81</v>
+      </c>
+      <c r="H6" s="21">
+        <v>158.67240000000001</v>
+      </c>
+      <c r="I6" s="43"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="43">
+        <f>G6</f>
+        <v>21.81</v>
+      </c>
+      <c r="L6" s="43">
+        <f>H6</f>
+        <v>158.67240000000001</v>
+      </c>
+      <c r="M6" s="22">
+        <v>433.51991556808798</v>
+      </c>
+      <c r="N6" s="22">
+        <v>18.259999998612201</v>
+      </c>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="22"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="19">
+        <v>1239</v>
+      </c>
+      <c r="C7" s="19">
+        <v>16</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="20">
+        <v>44893.572569444441</v>
+      </c>
+      <c r="F7" s="20">
+        <v>41166</v>
+      </c>
+      <c r="G7" s="43">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="H7" s="21">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="I7" s="43">
+        <f>I5</f>
+        <v>3.9999999999906777E-4</v>
+      </c>
+      <c r="J7" s="21">
+        <f>H7/G7*I7</f>
+        <v>2.8999999999932409E-3</v>
+      </c>
+      <c r="K7" s="21">
+        <f>G7-I7</f>
+        <v>9.3225123801166099E-16</v>
+      </c>
+      <c r="L7" s="21">
+        <f>H7-J7</f>
+        <v>6.7589163432746346E-15</v>
+      </c>
+      <c r="M7" s="22">
+        <v>433.54192724694099</v>
+      </c>
+      <c r="N7" s="22">
+        <v>18.259999998612201</v>
+      </c>
+      <c r="O7" s="22">
+        <f>$N7*J7</f>
+        <v>5.2953999995851965E-2</v>
+      </c>
+      <c r="P7" s="22">
+        <f>$N7*L7</f>
+        <v>1.2341781241881482E-13</v>
+      </c>
+      <c r="Q7" s="22">
+        <f>I5*M5-O7</f>
+        <v>0.13014284000372131</v>
+      </c>
+      <c r="R7" s="19"/>
+      <c r="S7" s="22">
+        <f>S$3/G5*G7</f>
+        <v>3.9421335050440015E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="48">
+        <v>1241</v>
+      </c>
+      <c r="C8" s="48">
+        <v>16</v>
+      </c>
+      <c r="D8" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="49">
+        <v>44939.567002314812</v>
+      </c>
+      <c r="F8" s="49">
+        <v>41166</v>
+      </c>
+      <c r="G8" s="50">
+        <v>2.0112999999999999</v>
+      </c>
+      <c r="H8" s="51">
+        <v>14.956799999999999</v>
+      </c>
+      <c r="I8" s="50"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="50">
+        <f>G8</f>
+        <v>2.0112999999999999</v>
+      </c>
+      <c r="L8" s="50">
+        <f>H8</f>
+        <v>14.956799999999999</v>
+      </c>
+      <c r="M8" s="52">
+        <v>434.45088886239699</v>
+      </c>
+      <c r="N8" s="52">
+        <v>18.259999998612201</v>
+      </c>
+      <c r="O8" s="52">
+        <f>$N8*J8</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="52">
+        <f>$N8*L8</f>
+        <v>273.11116797924296</v>
+      </c>
+      <c r="Q8" s="52">
+        <f>I4*M4-O8</f>
+        <v>0.17331323633192489</v>
+      </c>
+      <c r="R8" s="53">
+        <f>K8*M$16-P8</f>
+        <v>652.38772250075704</v>
+      </c>
+      <c r="S8" s="52"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="19">
+        <v>197</v>
+      </c>
+      <c r="C9" s="19">
+        <v>17</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="20">
+        <v>44473.584976851853</v>
+      </c>
+      <c r="F9" s="20">
+        <v>41377</v>
+      </c>
+      <c r="G9" s="43">
+        <v>24.54</v>
+      </c>
+      <c r="H9" s="21">
+        <v>226.48509999999999</v>
+      </c>
+      <c r="I9" s="43"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="43">
+        <f t="shared" ref="K9:L15" si="0">G9</f>
+        <v>24.54</v>
+      </c>
+      <c r="L9" s="43">
+        <f t="shared" si="0"/>
+        <v>226.48509999999999</v>
+      </c>
+      <c r="M9" s="22">
+        <v>435.10187449062698</v>
+      </c>
+      <c r="N9" s="22">
+        <v>19.7899983277443</v>
+      </c>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="22"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="48">
+        <v>1241</v>
+      </c>
+      <c r="C10" s="48">
+        <v>17</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="49">
+        <v>44939.567002314812</v>
+      </c>
+      <c r="F10" s="49">
+        <v>41377</v>
+      </c>
+      <c r="G10" s="50">
+        <v>1.1525000000000001</v>
+      </c>
+      <c r="H10" s="51">
+        <v>18.2224</v>
+      </c>
+      <c r="I10" s="50"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="50">
+        <f t="shared" si="0"/>
+        <v>1.1525000000000001</v>
+      </c>
+      <c r="L10" s="50">
+        <f t="shared" si="0"/>
+        <v>18.2224</v>
+      </c>
+      <c r="M10" s="52">
+        <v>434.45088886239699</v>
+      </c>
+      <c r="N10" s="52">
+        <v>19.7899983277443</v>
+      </c>
+      <c r="O10" s="52">
+        <f>$N10*J10</f>
+        <v>0</v>
+      </c>
+      <c r="P10" s="52">
+        <f>$N10*L10</f>
+        <v>360.62126552748776</v>
+      </c>
+      <c r="Q10" s="52">
+        <f>I11*M11-O10</f>
+        <v>0</v>
+      </c>
+      <c r="R10" s="53">
+        <f>K10*M$16-P10</f>
+        <v>169.70114847251233</v>
+      </c>
+      <c r="S10" s="52"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="19">
+        <v>205</v>
+      </c>
+      <c r="C11" s="19">
+        <v>17</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="20">
+        <v>44524.517384259256</v>
+      </c>
+      <c r="F11" s="20">
+        <v>41377</v>
+      </c>
+      <c r="G11" s="43">
+        <v>46.265999999999998</v>
+      </c>
+      <c r="H11" s="21">
+        <v>396.34890000000001</v>
+      </c>
+      <c r="I11" s="43"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="43">
+        <f t="shared" si="0"/>
+        <v>46.265999999999998</v>
+      </c>
+      <c r="L11" s="43">
+        <f t="shared" si="0"/>
+        <v>396.34890000000001</v>
+      </c>
+      <c r="M11" s="22">
+        <v>434.75770544244102</v>
+      </c>
+      <c r="N11" s="22">
+        <v>19.7899983277443</v>
+      </c>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="22"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="19">
+        <v>203</v>
+      </c>
+      <c r="C12" s="19">
+        <v>7</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="20">
+        <v>44496.480810185189</v>
+      </c>
+      <c r="F12" s="20">
+        <v>41492.000011574077</v>
+      </c>
+      <c r="G12" s="43">
+        <v>29.760999999999999</v>
+      </c>
+      <c r="H12" s="21">
+        <v>22.006</v>
+      </c>
+      <c r="I12" s="43"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="43">
+        <f t="shared" si="0"/>
+        <v>29.760999999999999</v>
+      </c>
+      <c r="L12" s="43">
+        <f t="shared" si="0"/>
+        <v>22.006</v>
+      </c>
+      <c r="M12" s="22">
+        <v>434.94679414813902</v>
+      </c>
+      <c r="N12" s="22">
+        <v>250.44122530300501</v>
+      </c>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="22"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="48">
+        <v>1241</v>
+      </c>
+      <c r="C13" s="48">
+        <v>27</v>
+      </c>
+      <c r="D13" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="49">
+        <v>44939.567002314812</v>
+      </c>
+      <c r="F13" s="49">
+        <v>41521</v>
+      </c>
+      <c r="G13" s="50">
+        <v>0.64380000000000004</v>
+      </c>
+      <c r="H13" s="51">
+        <v>13.0237</v>
+      </c>
+      <c r="I13" s="50"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="50">
+        <f t="shared" si="0"/>
+        <v>0.64380000000000004</v>
+      </c>
+      <c r="L13" s="50">
+        <f t="shared" si="0"/>
+        <v>13.0237</v>
+      </c>
+      <c r="M13" s="52">
+        <v>434.45088886239699</v>
+      </c>
+      <c r="N13" s="52">
+        <v>17.093261768828398</v>
+      </c>
+      <c r="O13" s="52">
+        <f>$N13*J13</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="52">
+        <f>$N13*L13</f>
+        <v>222.6175132986904</v>
+      </c>
+      <c r="Q13" s="52">
+        <f>I14*M14-O13</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="53">
+        <f>K13*M$16-P13</f>
+        <v>73.626799181309622</v>
+      </c>
+      <c r="S13" s="52"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="19">
+        <v>203</v>
+      </c>
+      <c r="C14" s="19">
+        <v>37</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="20">
+        <v>44496.480810185189</v>
+      </c>
+      <c r="F14" s="20">
+        <v>41534</v>
+      </c>
+      <c r="G14" s="43">
+        <v>4.9630000000000001</v>
+      </c>
+      <c r="H14" s="21">
+        <v>76.745999999999995</v>
+      </c>
+      <c r="I14" s="43"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="43">
+        <f t="shared" si="0"/>
+        <v>4.9630000000000001</v>
+      </c>
+      <c r="L14" s="43">
+        <f t="shared" si="0"/>
+        <v>76.745999999999995</v>
+      </c>
+      <c r="M14" s="22">
+        <v>434.94679414813902</v>
+      </c>
+      <c r="N14" s="22">
+        <v>13.029995048601901</v>
+      </c>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="22"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="48">
+        <v>1241</v>
+      </c>
+      <c r="C15" s="48">
+        <v>108</v>
+      </c>
+      <c r="D15" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="49">
+        <v>44939.567002314812</v>
+      </c>
+      <c r="F15" s="49">
+        <v>42387.492534722223</v>
+      </c>
+      <c r="G15" s="50">
+        <v>2.0644</v>
+      </c>
+      <c r="H15" s="51">
+        <v>0.53749999999999998</v>
+      </c>
+      <c r="I15" s="50"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="50">
+        <f t="shared" si="0"/>
+        <v>2.0644</v>
+      </c>
+      <c r="L15" s="50">
+        <f t="shared" si="0"/>
+        <v>0.53749999999999998</v>
+      </c>
+      <c r="M15" s="52">
+        <v>434.45088886239699</v>
+      </c>
+      <c r="N15" s="52">
+        <v>1860.4651162790601</v>
+      </c>
+      <c r="O15" s="52">
+        <f>$N15*J15</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="52">
+        <f>$N15*L15</f>
+        <v>999.99999999999477</v>
+      </c>
+      <c r="Q15" s="52">
+        <f>I16*M16-O15</f>
+        <v>0</v>
+      </c>
+      <c r="R15" s="53">
+        <f>K15*M$16-P15</f>
+        <v>-50.067165759994737</v>
+      </c>
+      <c r="S15" s="52"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="M16" s="27">
+        <v>460.14960000000002</v>
+      </c>
+      <c r="R16" s="47">
+        <f>SUM(R8:R15)</f>
+        <v>845.64850439458428</v>
+      </c>
+    </row>
+    <row r="17" spans="6:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q17" s="13"/>
+    </row>
+    <row r="18" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F18" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="30"/>
+      <c r="H18" s="31"/>
+    </row>
+    <row r="19" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F19" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="H19" s="41" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F20" s="34">
+        <v>36871</v>
+      </c>
+      <c r="G20" s="12">
+        <v>7.1680000000000001</v>
+      </c>
+      <c r="H20" s="35">
+        <v>3087.53</v>
+      </c>
+    </row>
+    <row r="21" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F21" s="34">
+        <v>36889</v>
+      </c>
+      <c r="G21" s="12">
+        <v>9.6880000000000006</v>
+      </c>
+      <c r="H21" s="35">
+        <v>3005.06</v>
+      </c>
+    </row>
+    <row r="22" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F22" s="34">
+        <v>36913</v>
+      </c>
+      <c r="G22" s="12">
+        <v>1.778</v>
+      </c>
+      <c r="H22" s="35">
+        <v>601.01</v>
+      </c>
+    </row>
+    <row r="23" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F23" s="34">
+        <v>41169</v>
+      </c>
+      <c r="G23" s="12">
+        <v>2E-3</v>
+      </c>
+      <c r="H23" s="35">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="24" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F24" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="33">
+        <f>SUM(G20:G23)</f>
+        <v>18.635999999999999</v>
+      </c>
+      <c r="H24" s="36">
+        <f>SUM(H20:H23)</f>
+        <v>6693.83</v>
+      </c>
+    </row>
+    <row r="25" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F25" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="H25" s="41" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="F26" s="34">
+        <v>45495</v>
+      </c>
+      <c r="G26" s="12">
+        <v>18.635999999999999</v>
+      </c>
+      <c r="H26" s="35">
+        <v>8530.48</v>
+      </c>
+    </row>
+    <row r="27" spans="6:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F27" s="37"/>
+      <c r="G27" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="39">
+        <f>H26-H24</f>
+        <v>1836.6499999999996</v>
+      </c>
+    </row>
+    <row r="28" spans="6:17" x14ac:dyDescent="0.35">
+      <c r="H28" s="28"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="19">
+        <v>217</v>
+      </c>
+      <c r="C35" s="19">
+        <v>16</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="20">
+        <v>44725.295381944445</v>
+      </c>
+      <c r="F35" s="20">
+        <v>41166</v>
+      </c>
+      <c r="G35" s="43">
+        <v>23.23</v>
+      </c>
+      <c r="H35" s="21">
+        <v>152.5463</v>
+      </c>
+      <c r="I35" s="43" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J35" s="21" t="e">
+        <f>H35/G35*I35</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K35" s="21" t="e">
+        <f>G35-I35</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L35" s="21" t="e">
+        <f>H35-J35</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M35" s="22">
+        <v>433.54192724694099</v>
+      </c>
+      <c r="N35" s="22">
+        <v>18.259999998612201</v>
+      </c>
+      <c r="O35" s="22" t="e">
+        <f>$N35*J35</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P35" s="22" t="e">
+        <f>$N35*L35</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q35" s="22" t="e">
+        <f>#REF!*#REF!-O35</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R35" s="19"/>
+      <c r="S35" s="22" t="e">
+        <f>S$3/#REF!*G35</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="19">
+        <v>1235</v>
+      </c>
+      <c r="C36" s="19">
+        <v>16</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" s="20">
+        <v>44893.559050925927</v>
+      </c>
+      <c r="F36" s="20">
+        <v>41166</v>
+      </c>
+      <c r="G36" s="43">
+        <v>21.81</v>
+      </c>
+      <c r="H36" s="21">
+        <v>158.67240000000001</v>
+      </c>
+      <c r="I36" s="50"/>
+      <c r="J36" s="51"/>
+      <c r="K36" s="50">
+        <f>G36</f>
+        <v>21.81</v>
+      </c>
+      <c r="L36" s="50">
+        <f>H36</f>
+        <v>158.67240000000001</v>
+      </c>
+      <c r="M36" s="52">
+        <v>434.45088886239699</v>
+      </c>
+      <c r="N36" s="52">
+        <v>18.259999998612201</v>
+      </c>
+      <c r="O36" s="52">
+        <f>$N36*J36</f>
+        <v>0</v>
+      </c>
+      <c r="P36" s="52">
+        <f>$N36*L36</f>
+        <v>2897.3580237797951</v>
+      </c>
+      <c r="Q36" s="52">
+        <f>I37*M37-O36</f>
+        <v>0</v>
+      </c>
+      <c r="R36" s="53">
+        <f>K36*M$16-P36</f>
+        <v>7138.5047522202049</v>
+      </c>
+      <c r="S36" s="52"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="19">
+        <v>1239</v>
+      </c>
+      <c r="C37" s="19">
+        <v>16</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E37" s="20">
+        <v>44893.572569444441</v>
+      </c>
+      <c r="F37" s="20">
+        <v>41166</v>
+      </c>
+      <c r="G37" s="43">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="H37" s="21">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="I37" s="43"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="43">
+        <f t="shared" ref="K37:L38" si="1">G37</f>
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="L37" s="43">
+        <f t="shared" si="1"/>
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="M37" s="22">
+        <v>433.283090830822</v>
+      </c>
+      <c r="N37" s="22">
+        <v>18.259999998612201</v>
+      </c>
+      <c r="O37" s="19"/>
+      <c r="P37" s="19"/>
+      <c r="Q37" s="19"/>
+      <c r="R37" s="19"/>
+      <c r="S37" s="22"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="48">
+        <v>1241</v>
+      </c>
+      <c r="C38" s="48">
+        <v>16</v>
+      </c>
+      <c r="D38" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="E38" s="49">
+        <v>44939.567002314812</v>
+      </c>
+      <c r="F38" s="49">
+        <v>41166</v>
+      </c>
+      <c r="G38" s="50">
+        <v>2.0112999999999999</v>
+      </c>
+      <c r="H38" s="51">
+        <v>14.956799999999999</v>
+      </c>
+      <c r="I38" s="43"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="43">
+        <f t="shared" si="1"/>
+        <v>2.0112999999999999</v>
+      </c>
+      <c r="L38" s="43">
+        <f t="shared" si="1"/>
+        <v>14.956799999999999</v>
+      </c>
+      <c r="M38" s="22">
+        <v>433.51991556808798</v>
+      </c>
+      <c r="N38" s="22">
+        <v>18.259999998612201</v>
+      </c>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="19"/>
+      <c r="R38" s="19"/>
+      <c r="S38" s="22"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>